--- a/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_clark4F(1).xlsx
+++ b/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_clark4F(1).xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="20685" windowHeight="11400"/>
   </bookViews>
   <sheets>
     <sheet name="圣诺汀之梦_克拉克线4层（上）" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1028" uniqueCount="396">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1015" uniqueCount="395">
   <si>
     <t>ID</t>
   </si>
@@ -84,6 +84,9 @@
     <t/>
   </si>
   <si>
+    <t>9 enhanced suspense tensions</t>
+  </si>
+  <si>
     <t>false</t>
   </si>
   <si>
@@ -99,7 +102,15 @@
     <t>它迟早会出来的，我们必须尽快去到楼上。</t>
   </si>
   <si>
+    <t>stop</t>
+  </si>
+  <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>源类型</t>
     </r>
     <r>
@@ -157,6 +168,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>源类型</t>
     </r>
     <r>
@@ -731,6 +747,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
       <t>loadScript(</t>
     </r>
     <r>
@@ -781,19 +802,10 @@
     <t>11</t>
   </si>
   <si>
-    <t>不到半分钟的功夫，你们便来到了四楼空旷无人的半露天平台上。四周的环境安静得有些发冷，从1层至4层</t>
+    <t>不到半分钟的功夫，你们便来到了四楼空旷无人的半露天平台上。四周的环境安静得有些发冷，一路上畅通无阻的顺利，反而让你们不自觉绷紧了神经。</t>
   </si>
   <si>
     <t>源类型=type:txt_pb; 层级=1; wherelist={"wheretype":"1","wheredatas":[{"sortnum":"1","way":"=","conditions":[{"algorithm":"+","valuetype":"4","valuekey":"","valuedata":"无视飞蛾（克拉克）","dowlist4":[]}],"targets":[{"algorithm":"+","valuetype":"1","valuekey":"","valuedata":"0","dowlist4":[]}]}]}</t>
-  </si>
-  <si>
-    <t>65</t>
-  </si>
-  <si>
-    <t>不到半分钟的功夫，你们便来到了四楼空旷无人的半露天平台上。四周的环境安静得有些发冷，一路上畅通无阻的顺利，反而让你们不自觉绷紧了神经。</t>
-  </si>
-  <si>
-    <t>源类型=type:txt_pb; 层级=2</t>
   </si>
   <si>
     <t>66</t>
@@ -2544,7 +2556,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L68"/>
+  <dimension ref="A1:L67"/>
   <sheetFormatPr defaultColWidth="10.2857142857143" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -2595,7 +2607,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" ht="30" spans="1:12">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -2621,24 +2633,24 @@
         <v>15</v>
       </c>
       <c r="I2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K2" t="s">
         <v>15</v>
       </c>
       <c r="L2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3" ht="90" spans="1:12">
       <c r="A3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C3" t="s">
         <v>14</v>
@@ -2653,13 +2665,13 @@
         <v>15</v>
       </c>
       <c r="G3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="H3" t="s">
         <v>15</v>
       </c>
       <c r="I3" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="J3" t="s">
         <v>15</v>
@@ -2668,12 +2680,12 @@
         <v>15</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B4" t="s">
         <v>13</v>
@@ -2706,12 +2718,12 @@
         <v>15</v>
       </c>
       <c r="L4" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" ht="150" spans="1:12">
       <c r="A5" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B5" t="s">
         <v>13</v>
@@ -2729,7 +2741,7 @@
         <v>15</v>
       </c>
       <c r="G5" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="H5" t="s">
         <v>15</v>
@@ -2744,12 +2756,12 @@
         <v>15</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6" ht="54" spans="1:12">
       <c r="A6" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B6" t="s">
         <v>13</v>
@@ -2767,7 +2779,7 @@
         <v>15</v>
       </c>
       <c r="G6" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H6" t="s">
         <v>15</v>
@@ -2779,24 +2791,24 @@
         <v>15</v>
       </c>
       <c r="K6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="L6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="7" ht="150" spans="1:12">
       <c r="A7" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B7" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C7" t="s">
         <v>14</v>
       </c>
       <c r="D7" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E7" t="s">
         <v>15</v>
@@ -2805,7 +2817,7 @@
         <v>15</v>
       </c>
       <c r="G7" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H7" t="s">
         <v>15</v>
@@ -2817,24 +2829,24 @@
         <v>15</v>
       </c>
       <c r="K7" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="L7" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="8" ht="30" spans="1:12">
       <c r="A8" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C8" t="s">
         <v>14</v>
       </c>
       <c r="D8" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E8" t="s">
         <v>15</v>
@@ -2843,7 +2855,7 @@
         <v>15</v>
       </c>
       <c r="G8" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="H8" t="s">
         <v>15</v>
@@ -2855,15 +2867,15 @@
         <v>15</v>
       </c>
       <c r="K8" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="L8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="9" ht="54" spans="1:12">
       <c r="A9" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B9" t="s">
         <v>13</v>
@@ -2881,7 +2893,7 @@
         <v>15</v>
       </c>
       <c r="G9" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="H9" t="s">
         <v>15</v>
@@ -2896,21 +2908,21 @@
         <v>15</v>
       </c>
       <c r="L9" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="10" ht="30" spans="1:12">
       <c r="A10" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B10" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C10" t="s">
         <v>14</v>
       </c>
       <c r="D10" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E10" t="s">
         <v>15</v>
@@ -2919,7 +2931,7 @@
         <v>15</v>
       </c>
       <c r="G10" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H10" t="s">
         <v>15</v>
@@ -2931,15 +2943,15 @@
         <v>15</v>
       </c>
       <c r="K10" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="L10" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="11" ht="54" spans="1:12">
       <c r="A11" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="B11" t="s">
         <v>13</v>
@@ -2948,7 +2960,7 @@
         <v>14</v>
       </c>
       <c r="D11" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E11" t="s">
         <v>15</v>
@@ -2957,7 +2969,7 @@
         <v>15</v>
       </c>
       <c r="G11" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H11" t="s">
         <v>15</v>
@@ -2969,24 +2981,24 @@
         <v>15</v>
       </c>
       <c r="K11" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="L11" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="12" ht="27" spans="1:12">
       <c r="A12" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B12" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C12" t="s">
         <v>14</v>
       </c>
       <c r="D12" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E12" t="s">
         <v>15</v>
@@ -2995,7 +3007,7 @@
         <v>15</v>
       </c>
       <c r="G12" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="H12" t="s">
         <v>15</v>
@@ -3007,24 +3019,24 @@
         <v>15</v>
       </c>
       <c r="K12" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="L12" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="13" ht="27" spans="1:12">
       <c r="A13" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B13" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C13" t="s">
         <v>14</v>
       </c>
       <c r="D13" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E13" t="s">
         <v>15</v>
@@ -3033,7 +3045,7 @@
         <v>15</v>
       </c>
       <c r="G13" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="H13" t="s">
         <v>15</v>
@@ -3048,12 +3060,12 @@
         <v>15</v>
       </c>
       <c r="L13" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14" ht="27" spans="1:12">
       <c r="A14" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B14" t="s">
         <v>13</v>
@@ -3062,7 +3074,7 @@
         <v>14</v>
       </c>
       <c r="D14" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E14" t="s">
         <v>15</v>
@@ -3071,7 +3083,7 @@
         <v>15</v>
       </c>
       <c r="G14" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="H14" t="s">
         <v>15</v>
@@ -3083,15 +3095,15 @@
         <v>15</v>
       </c>
       <c r="K14" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="L14" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="15" spans="1:12">
       <c r="A15" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B15" t="s">
         <v>13</v>
@@ -3124,21 +3136,21 @@
         <v>15</v>
       </c>
       <c r="L15" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="16" ht="90" spans="1:12">
       <c r="A16" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B16" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C16" t="s">
         <v>14</v>
       </c>
       <c r="D16" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E16" t="s">
         <v>15</v>
@@ -3147,7 +3159,7 @@
         <v>15</v>
       </c>
       <c r="G16" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="H16" t="s">
         <v>15</v>
@@ -3159,15 +3171,15 @@
         <v>15</v>
       </c>
       <c r="K16" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="L16" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="17" ht="30" spans="1:12">
       <c r="A17" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B17" t="s">
         <v>13</v>
@@ -3176,7 +3188,7 @@
         <v>14</v>
       </c>
       <c r="D17" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E17" t="s">
         <v>15</v>
@@ -3185,7 +3197,7 @@
         <v>15</v>
       </c>
       <c r="G17" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H17" t="s">
         <v>15</v>
@@ -3197,15 +3209,15 @@
         <v>15</v>
       </c>
       <c r="K17" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="L17" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="18" ht="45" spans="1:12">
       <c r="A18" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B18" t="s">
         <v>13</v>
@@ -3235,15 +3247,15 @@
         <v>15</v>
       </c>
       <c r="K18" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="L18" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="19" spans="1:12">
       <c r="A19" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B19" t="s">
         <v>13</v>
@@ -3276,15 +3288,15 @@
         <v>15</v>
       </c>
       <c r="L19" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="20" ht="42" spans="1:12">
       <c r="A20" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B20" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C20" t="s">
         <v>14</v>
@@ -3299,7 +3311,7 @@
         <v>15</v>
       </c>
       <c r="G20" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H20" t="s">
         <v>15</v>
@@ -3314,21 +3326,21 @@
         <v>15</v>
       </c>
       <c r="L20" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="21" ht="30" spans="1:12">
       <c r="A21" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B21" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C21" t="s">
         <v>14</v>
       </c>
       <c r="D21" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E21" t="s">
         <v>15</v>
@@ -3337,7 +3349,7 @@
         <v>15</v>
       </c>
       <c r="G21" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="H21" t="s">
         <v>15</v>
@@ -3349,15 +3361,15 @@
         <v>15</v>
       </c>
       <c r="K21" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="L21" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
     </row>
     <row r="22" ht="40.5" spans="1:12">
       <c r="A22" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B22" t="s">
         <v>13</v>
@@ -3366,7 +3378,7 @@
         <v>14</v>
       </c>
       <c r="D22" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E22" t="s">
         <v>15</v>
@@ -3375,7 +3387,7 @@
         <v>15</v>
       </c>
       <c r="G22" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H22" t="s">
         <v>15</v>
@@ -3387,18 +3399,18 @@
         <v>15</v>
       </c>
       <c r="K22" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="L22" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="23" ht="57" spans="1:12">
       <c r="A23" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B23" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C23" t="s">
         <v>14</v>
@@ -3413,7 +3425,7 @@
         <v>15</v>
       </c>
       <c r="G23" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H23" t="s">
         <v>15</v>
@@ -3428,12 +3440,12 @@
         <v>15</v>
       </c>
       <c r="L23" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="24" ht="27" spans="1:12">
       <c r="A24" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B24" t="s">
         <v>13</v>
@@ -3451,7 +3463,7 @@
         <v>15</v>
       </c>
       <c r="G24" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H24" t="s">
         <v>15</v>
@@ -3466,15 +3478,15 @@
         <v>15</v>
       </c>
       <c r="L24" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="25" spans="1:12">
       <c r="A25" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B25" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C25" t="s">
         <v>14</v>
@@ -3489,7 +3501,7 @@
         <v>15</v>
       </c>
       <c r="G25" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="H25" t="s">
         <v>15</v>
@@ -3504,15 +3516,15 @@
         <v>15</v>
       </c>
       <c r="L25" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="26" spans="1:12">
       <c r="A26" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B26" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C26" t="s">
         <v>14</v>
@@ -3527,7 +3539,7 @@
         <v>15</v>
       </c>
       <c r="G26" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="H26" t="s">
         <v>15</v>
@@ -3542,12 +3554,12 @@
         <v>15</v>
       </c>
       <c r="L26" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="27" ht="40.5" spans="1:12">
       <c r="A27" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B27" t="s">
         <v>13</v>
@@ -3565,7 +3577,7 @@
         <v>15</v>
       </c>
       <c r="G27" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="H27" t="s">
         <v>15</v>
@@ -3580,12 +3592,12 @@
         <v>15</v>
       </c>
       <c r="L27" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="28" ht="27" spans="1:12">
       <c r="A28" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B28" t="s">
         <v>13</v>
@@ -3603,7 +3615,7 @@
         <v>15</v>
       </c>
       <c r="G28" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="H28" t="s">
         <v>15</v>
@@ -3618,12 +3630,12 @@
         <v>15</v>
       </c>
       <c r="L28" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="29" spans="1:12">
       <c r="A29" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B29" t="s">
         <v>13</v>
@@ -3656,12 +3668,12 @@
         <v>15</v>
       </c>
       <c r="L29" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="30" ht="90" spans="1:12">
       <c r="A30" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B30" t="s">
         <v>13</v>
@@ -3679,7 +3691,7 @@
         <v>15</v>
       </c>
       <c r="G30" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="H30" t="s">
         <v>15</v>
@@ -3691,15 +3703,15 @@
         <v>15</v>
       </c>
       <c r="K30" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="L30" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="31" ht="90" spans="1:12">
       <c r="A31" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B31" t="s">
         <v>13</v>
@@ -3717,7 +3729,7 @@
         <v>15</v>
       </c>
       <c r="G31" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="H31" t="s">
         <v>15</v>
@@ -3729,15 +3741,15 @@
         <v>15</v>
       </c>
       <c r="K31" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="L31" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="32" spans="1:12">
       <c r="A32" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B32" t="s">
         <v>13</v>
@@ -3770,15 +3782,15 @@
         <v>15</v>
       </c>
       <c r="L32" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="33" ht="54" spans="1:12">
       <c r="A33" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B33" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C33" t="s">
         <v>14</v>
@@ -3793,7 +3805,7 @@
         <v>15</v>
       </c>
       <c r="G33" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="H33" t="s">
         <v>15</v>
@@ -3808,12 +3820,12 @@
         <v>15</v>
       </c>
       <c r="L33" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="34" ht="54" spans="1:12">
       <c r="A34" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B34" t="s">
         <v>13</v>
@@ -3831,7 +3843,7 @@
         <v>15</v>
       </c>
       <c r="G34" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="H34" t="s">
         <v>15</v>
@@ -3846,21 +3858,21 @@
         <v>15</v>
       </c>
       <c r="L34" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="35" ht="40.5" spans="1:12">
       <c r="A35" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B35" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C35" t="s">
         <v>14</v>
       </c>
       <c r="D35" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E35" t="s">
         <v>15</v>
@@ -3869,7 +3881,7 @@
         <v>15</v>
       </c>
       <c r="G35" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="H35" t="s">
         <v>15</v>
@@ -3881,24 +3893,24 @@
         <v>15</v>
       </c>
       <c r="K35" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="L35" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
     <row r="36" ht="30" spans="1:12">
       <c r="A36" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B36" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C36" t="s">
         <v>14</v>
       </c>
       <c r="D36" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E36" t="s">
         <v>15</v>
@@ -3907,7 +3919,7 @@
         <v>15</v>
       </c>
       <c r="G36" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="H36" t="s">
         <v>15</v>
@@ -3922,12 +3934,12 @@
         <v>15</v>
       </c>
       <c r="L36" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="37" ht="54" spans="1:12">
       <c r="A37" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B37" t="s">
         <v>13</v>
@@ -3936,7 +3948,7 @@
         <v>14</v>
       </c>
       <c r="D37" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E37" t="s">
         <v>15</v>
@@ -3945,7 +3957,7 @@
         <v>15</v>
       </c>
       <c r="G37" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="H37" t="s">
         <v>15</v>
@@ -3957,15 +3969,15 @@
         <v>15</v>
       </c>
       <c r="K37" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="L37" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="38" ht="40.5" spans="1:12">
       <c r="A38" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B38" t="s">
         <v>13</v>
@@ -3983,7 +3995,7 @@
         <v>15</v>
       </c>
       <c r="G38" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="H38" t="s">
         <v>15</v>
@@ -3998,12 +4010,12 @@
         <v>15</v>
       </c>
       <c r="L38" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="39" ht="27" spans="1:12">
       <c r="A39" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B39" t="s">
         <v>13</v>
@@ -4021,7 +4033,7 @@
         <v>15</v>
       </c>
       <c r="G39" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="H39" t="s">
         <v>15</v>
@@ -4033,15 +4045,15 @@
         <v>15</v>
       </c>
       <c r="K39" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="L39" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
     </row>
     <row r="40" ht="40.5" spans="1:12">
       <c r="A40" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B40" t="s">
         <v>13</v>
@@ -4059,7 +4071,7 @@
         <v>15</v>
       </c>
       <c r="G40" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="H40" t="s">
         <v>15</v>
@@ -4074,12 +4086,12 @@
         <v>15</v>
       </c>
       <c r="L40" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="41" ht="43.5" spans="1:12">
       <c r="A41" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B41" t="s">
         <v>13</v>
@@ -4097,7 +4109,7 @@
         <v>15</v>
       </c>
       <c r="G41" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="H41" t="s">
         <v>15</v>
@@ -4112,12 +4124,12 @@
         <v>15</v>
       </c>
       <c r="L41" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="42" spans="1:12">
       <c r="A42" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B42" t="s">
         <v>13</v>
@@ -4150,12 +4162,12 @@
         <v>15</v>
       </c>
       <c r="L42" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="43" ht="90" spans="1:12">
       <c r="A43" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B43" t="s">
         <v>13</v>
@@ -4173,7 +4185,7 @@
         <v>15</v>
       </c>
       <c r="G43" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H43" t="s">
         <v>15</v>
@@ -4185,15 +4197,15 @@
         <v>15</v>
       </c>
       <c r="K43" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="L43" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="44" ht="90" spans="1:12">
       <c r="A44" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B44" t="s">
         <v>13</v>
@@ -4211,7 +4223,7 @@
         <v>15</v>
       </c>
       <c r="G44" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="H44" t="s">
         <v>15</v>
@@ -4226,21 +4238,21 @@
         <v>15</v>
       </c>
       <c r="L44" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
     </row>
     <row r="45" ht="40.5" spans="1:12">
       <c r="A45" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B45" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C45" t="s">
         <v>14</v>
       </c>
       <c r="D45" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E45" t="s">
         <v>15</v>
@@ -4249,7 +4261,7 @@
         <v>15</v>
       </c>
       <c r="G45" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="H45" t="s">
         <v>15</v>
@@ -4264,12 +4276,12 @@
         <v>15</v>
       </c>
       <c r="L45" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
     </row>
     <row r="46" ht="30" spans="1:12">
       <c r="A46" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="B46" t="s">
         <v>13</v>
@@ -4278,7 +4290,7 @@
         <v>14</v>
       </c>
       <c r="D46" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E46" t="s">
         <v>15</v>
@@ -4287,7 +4299,7 @@
         <v>15</v>
       </c>
       <c r="G46" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="H46" t="s">
         <v>15</v>
@@ -4299,21 +4311,21 @@
         <v>15</v>
       </c>
       <c r="L46" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="47" ht="30" spans="1:12">
       <c r="A47" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B47" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C47" t="s">
         <v>14</v>
       </c>
       <c r="D47" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E47" t="s">
         <v>15</v>
@@ -4322,7 +4334,7 @@
         <v>15</v>
       </c>
       <c r="G47" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="H47" t="s">
         <v>15</v>
@@ -4334,15 +4346,15 @@
         <v>15</v>
       </c>
       <c r="K47" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="L47" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="48" ht="90" spans="1:12">
       <c r="A48" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="B48" t="s">
         <v>13</v>
@@ -4351,7 +4363,7 @@
         <v>14</v>
       </c>
       <c r="D48" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E48" t="s">
         <v>15</v>
@@ -4360,7 +4372,7 @@
         <v>15</v>
       </c>
       <c r="G48" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="H48" t="s">
         <v>15</v>
@@ -4372,15 +4384,15 @@
         <v>15</v>
       </c>
       <c r="K48" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="L48" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
     </row>
     <row r="49" ht="40.5" spans="1:12">
       <c r="A49" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B49" t="s">
         <v>13</v>
@@ -4398,7 +4410,7 @@
         <v>15</v>
       </c>
       <c r="G49" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="H49" t="s">
         <v>15</v>
@@ -4413,12 +4425,12 @@
         <v>15</v>
       </c>
       <c r="L49" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="50" ht="27" spans="1:12">
       <c r="A50" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B50" t="s">
         <v>13</v>
@@ -4436,7 +4448,7 @@
         <v>15</v>
       </c>
       <c r="G50" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="H50" t="s">
         <v>15</v>
@@ -4451,12 +4463,12 @@
         <v>15</v>
       </c>
       <c r="L50" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="51" ht="40.5" spans="1:12">
       <c r="A51" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B51" t="s">
         <v>13</v>
@@ -4474,7 +4486,7 @@
         <v>15</v>
       </c>
       <c r="G51" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="H51" t="s">
         <v>15</v>
@@ -4489,12 +4501,12 @@
         <v>15</v>
       </c>
       <c r="L51" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="52" ht="40.5" spans="1:12">
       <c r="A52" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B52" t="s">
         <v>13</v>
@@ -4512,7 +4524,7 @@
         <v>15</v>
       </c>
       <c r="G52" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="H52" t="s">
         <v>15</v>
@@ -4524,18 +4536,18 @@
         <v>15</v>
       </c>
       <c r="K52" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="L52" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="53" spans="1:12">
       <c r="A53" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B53" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C53" t="s">
         <v>14</v>
@@ -4550,7 +4562,7 @@
         <v>15</v>
       </c>
       <c r="G53" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H53" t="s">
         <v>15</v>
@@ -4565,12 +4577,12 @@
         <v>15</v>
       </c>
       <c r="L53" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="54" ht="27" spans="1:12">
       <c r="A54" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B54" t="s">
         <v>13</v>
@@ -4588,7 +4600,7 @@
         <v>15</v>
       </c>
       <c r="G54" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H54" t="s">
         <v>15</v>
@@ -4603,12 +4615,12 @@
         <v>15</v>
       </c>
       <c r="L54" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="55" spans="1:12">
       <c r="A55" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B55" t="s">
         <v>13</v>
@@ -4641,12 +4653,12 @@
         <v>15</v>
       </c>
       <c r="L55" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="56" ht="90" spans="1:12">
       <c r="A56" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B56" t="s">
         <v>13</v>
@@ -4664,7 +4676,7 @@
         <v>15</v>
       </c>
       <c r="G56" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="H56" t="s">
         <v>15</v>
@@ -4679,12 +4691,12 @@
         <v>15</v>
       </c>
       <c r="L56" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="57" ht="40.5" spans="1:12">
       <c r="A57" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B57" t="s">
         <v>13</v>
@@ -4702,7 +4714,7 @@
         <v>15</v>
       </c>
       <c r="G57" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="H57" t="s">
         <v>15</v>
@@ -4717,12 +4729,12 @@
         <v>15</v>
       </c>
       <c r="L57" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
     </row>
     <row r="58" ht="40.5" spans="1:12">
       <c r="A58" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B58" t="s">
         <v>13</v>
@@ -4740,7 +4752,7 @@
         <v>15</v>
       </c>
       <c r="G58" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="H58" t="s">
         <v>15</v>
@@ -4755,12 +4767,12 @@
         <v>15</v>
       </c>
       <c r="L58" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="59" ht="55.5" spans="1:12">
       <c r="A59" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B59" t="s">
         <v>13</v>
@@ -4778,7 +4790,7 @@
         <v>15</v>
       </c>
       <c r="G59" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="H59" t="s">
         <v>15</v>
@@ -4793,12 +4805,12 @@
         <v>15</v>
       </c>
       <c r="L59" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="60" ht="42" spans="1:12">
       <c r="A60" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B60" t="s">
         <v>13</v>
@@ -4816,7 +4828,7 @@
         <v>15</v>
       </c>
       <c r="G60" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="H60" t="s">
         <v>15</v>
@@ -4831,12 +4843,12 @@
         <v>15</v>
       </c>
       <c r="L60" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="61" spans="1:12">
       <c r="A61" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B61" t="s">
         <v>13</v>
@@ -4854,7 +4866,7 @@
         <v>15</v>
       </c>
       <c r="G61" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="H61" t="s">
         <v>15</v>
@@ -4866,15 +4878,15 @@
         <v>15</v>
       </c>
       <c r="K61" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="L61" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="62" ht="42" spans="1:12">
       <c r="A62" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="B62" t="s">
         <v>13</v>
@@ -4892,27 +4904,25 @@
         <v>15</v>
       </c>
       <c r="G62" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="H62" t="s">
         <v>15</v>
       </c>
-      <c r="I62" t="s">
-        <v>15</v>
-      </c>
+      <c r="I62"/>
       <c r="J62" t="s">
         <v>15</v>
       </c>
       <c r="K62" s="3" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="L62" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
     <row r="63" ht="90" spans="1:12">
       <c r="A63" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B63" t="s">
         <v>13</v>
@@ -4930,7 +4940,7 @@
         <v>15</v>
       </c>
       <c r="G63" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="H63" t="s">
         <v>15</v>
@@ -4942,24 +4952,24 @@
         <v>15</v>
       </c>
       <c r="K63" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="L63" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
     </row>
     <row r="64" ht="90" spans="1:12">
       <c r="A64" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="B64" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C64" t="s">
         <v>14</v>
       </c>
       <c r="D64" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E64" t="s">
         <v>15</v>
@@ -4968,7 +4978,7 @@
         <v>15</v>
       </c>
       <c r="G64" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="H64" t="s">
         <v>15</v>
@@ -4980,15 +4990,15 @@
         <v>15</v>
       </c>
       <c r="K64" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="L64" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
     </row>
     <row r="65" ht="90" spans="1:12">
       <c r="A65" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B65" t="s">
         <v>13</v>
@@ -5006,7 +5016,7 @@
         <v>15</v>
       </c>
       <c r="G65" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="H65" t="s">
         <v>15</v>
@@ -5018,54 +5028,54 @@
         <v>15</v>
       </c>
       <c r="L65" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="66" ht="54" spans="1:12">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="66" spans="1:12">
       <c r="A66" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B66" t="s">
+        <v>20</v>
+      </c>
+      <c r="C66" t="s">
+        <v>14</v>
+      </c>
+      <c r="D66" t="s">
+        <v>15</v>
+      </c>
+      <c r="E66" t="s">
+        <v>15</v>
+      </c>
+      <c r="F66" t="s">
+        <v>15</v>
+      </c>
+      <c r="G66" t="s">
+        <v>214</v>
+      </c>
+      <c r="H66" t="s">
+        <v>15</v>
+      </c>
+      <c r="I66" t="s">
+        <v>15</v>
+      </c>
+      <c r="J66" t="s">
+        <v>15</v>
+      </c>
+      <c r="K66" t="s">
+        <v>15</v>
+      </c>
+      <c r="L66" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="67" ht="40.5" spans="1:12">
+      <c r="A67" t="s">
+        <v>216</v>
+      </c>
+      <c r="B67" t="s">
         <v>13</v>
       </c>
-      <c r="C66" t="s">
-        <v>14</v>
-      </c>
-      <c r="D66" t="s">
-        <v>15</v>
-      </c>
-      <c r="E66" t="s">
-        <v>15</v>
-      </c>
-      <c r="F66" t="s">
-        <v>15</v>
-      </c>
-      <c r="G66" t="s">
-        <v>212</v>
-      </c>
-      <c r="H66" t="s">
-        <v>15</v>
-      </c>
-      <c r="I66" t="s">
-        <v>15</v>
-      </c>
-      <c r="J66" t="s">
-        <v>15</v>
-      </c>
-      <c r="K66" t="s">
-        <v>15</v>
-      </c>
-      <c r="L66" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="67" spans="1:12">
-      <c r="A67" t="s">
-        <v>214</v>
-      </c>
-      <c r="B67" t="s">
-        <v>19</v>
-      </c>
       <c r="C67" t="s">
         <v>14</v>
       </c>
@@ -5079,7 +5089,7 @@
         <v>15</v>
       </c>
       <c r="G67" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="H67" t="s">
         <v>15</v>
@@ -5091,48 +5101,10 @@
         <v>15</v>
       </c>
       <c r="K67" t="s">
-        <v>15</v>
+        <v>108</v>
       </c>
       <c r="L67" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="68" ht="40.5" spans="1:12">
-      <c r="A68" t="s">
-        <v>217</v>
-      </c>
-      <c r="B68" t="s">
-        <v>13</v>
-      </c>
-      <c r="C68" t="s">
-        <v>14</v>
-      </c>
-      <c r="D68" t="s">
-        <v>15</v>
-      </c>
-      <c r="E68" t="s">
-        <v>15</v>
-      </c>
-      <c r="F68" t="s">
-        <v>15</v>
-      </c>
-      <c r="G68" t="s">
         <v>218</v>
-      </c>
-      <c r="H68" t="s">
-        <v>15</v>
-      </c>
-      <c r="I68" t="s">
-        <v>15</v>
-      </c>
-      <c r="J68" t="s">
-        <v>15</v>
-      </c>
-      <c r="K68" t="s">
-        <v>106</v>
-      </c>
-      <c r="L68" t="s">
-        <v>219</v>
       </c>
     </row>
   </sheetData>
@@ -5153,39 +5125,39 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>220</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>221</v>
       </c>
     </row>
     <row r="2" ht="45" spans="1:2">
       <c r="A2" t="s">
+        <v>221</v>
+      </c>
+      <c r="B2" t="s">
         <v>222</v>
-      </c>
-      <c r="B2" t="s">
-        <v>223</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
+        <v>223</v>
+      </c>
+      <c r="B3" t="s">
         <v>224</v>
-      </c>
-      <c r="B3" t="s">
-        <v>225</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B4" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B5" t="s">
         <v>12</v>
@@ -5193,15 +5165,15 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B6" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="7" ht="27" spans="1:2">
       <c r="A7" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B7" t="s">
         <v>12</v>
@@ -5209,66 +5181,66 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B8" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="9" ht="27" spans="1:2">
       <c r="A9" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B9" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="10" ht="75" spans="1:2">
       <c r="A10" t="s">
+        <v>231</v>
+      </c>
+      <c r="B10" t="s">
         <v>232</v>
-      </c>
-      <c r="B10" t="s">
-        <v>233</v>
       </c>
     </row>
     <row r="11" ht="75" spans="1:2">
       <c r="A11" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B11" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="12" ht="57" spans="1:2">
       <c r="A12" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B12" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="13" ht="58.5" spans="1:2">
       <c r="A13" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B13" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="14" ht="60" spans="1:2">
       <c r="A14" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B14" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="15" ht="75" spans="1:2">
       <c r="A15" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B15" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
   </sheetData>
@@ -5290,616 +5262,616 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>240</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>243</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>244</v>
       </c>
     </row>
     <row r="2" ht="73.5" spans="1:6">
       <c r="A2" t="s">
+        <v>244</v>
+      </c>
+      <c r="B2" t="s">
         <v>245</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>246</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>247</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>248</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>249</v>
-      </c>
-      <c r="F2" t="s">
-        <v>250</v>
       </c>
     </row>
     <row r="3" ht="103.5" spans="1:6">
       <c r="A3" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B3" t="s">
+        <v>250</v>
+      </c>
+      <c r="C3" t="s">
         <v>251</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>252</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>253</v>
       </c>
-      <c r="E3" t="s">
+      <c r="F3" t="s">
         <v>254</v>
-      </c>
-      <c r="F3" t="s">
-        <v>255</v>
       </c>
     </row>
     <row r="4" ht="45" spans="1:6">
       <c r="A4" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B4" t="s">
+        <v>255</v>
+      </c>
+      <c r="C4" t="s">
         <v>256</v>
       </c>
-      <c r="C4" t="s">
+      <c r="D4" t="s">
         <v>257</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
         <v>258</v>
       </c>
-      <c r="E4" t="s">
+      <c r="F4" t="s">
         <v>259</v>
-      </c>
-      <c r="F4" t="s">
-        <v>260</v>
       </c>
     </row>
     <row r="5" ht="45" spans="1:6">
       <c r="A5" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B5" t="s">
+        <v>260</v>
+      </c>
+      <c r="C5" t="s">
         <v>261</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
         <v>262</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>263</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
         <v>264</v>
-      </c>
-      <c r="F5" t="s">
-        <v>265</v>
       </c>
     </row>
     <row r="6" ht="45" spans="1:6">
       <c r="A6" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B6" t="s">
+        <v>265</v>
+      </c>
+      <c r="C6" t="s">
         <v>266</v>
       </c>
-      <c r="C6" t="s">
+      <c r="D6" t="s">
         <v>267</v>
       </c>
-      <c r="D6" t="s">
+      <c r="E6" t="s">
         <v>268</v>
       </c>
-      <c r="E6" t="s">
+      <c r="F6" t="s">
         <v>269</v>
-      </c>
-      <c r="F6" t="s">
-        <v>270</v>
       </c>
     </row>
     <row r="7" ht="75" spans="1:6">
       <c r="A7" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B7" t="s">
+        <v>270</v>
+      </c>
+      <c r="C7" t="s">
         <v>271</v>
       </c>
-      <c r="C7" t="s">
+      <c r="D7" t="s">
         <v>272</v>
       </c>
-      <c r="D7" t="s">
+      <c r="E7" t="s">
         <v>273</v>
       </c>
-      <c r="E7" t="s">
+      <c r="F7" t="s">
         <v>274</v>
-      </c>
-      <c r="F7" t="s">
-        <v>275</v>
       </c>
     </row>
     <row r="8" ht="45" spans="1:6">
       <c r="A8" t="s">
+        <v>275</v>
+      </c>
+      <c r="B8" t="s">
         <v>276</v>
       </c>
-      <c r="B8" t="s">
+      <c r="C8" t="s">
         <v>277</v>
       </c>
-      <c r="C8" t="s">
+      <c r="D8" t="s">
         <v>278</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" t="s">
         <v>279</v>
       </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
         <v>280</v>
-      </c>
-      <c r="F8" t="s">
-        <v>281</v>
       </c>
     </row>
     <row r="9" ht="45" spans="1:6">
       <c r="A9" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B9" t="s">
+        <v>281</v>
+      </c>
+      <c r="C9" t="s">
         <v>282</v>
       </c>
-      <c r="C9" t="s">
+      <c r="D9" t="s">
         <v>283</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>284</v>
       </c>
-      <c r="E9" t="s">
+      <c r="F9" t="s">
         <v>285</v>
-      </c>
-      <c r="F9" t="s">
-        <v>286</v>
       </c>
     </row>
     <row r="10" ht="58.5" spans="1:6">
       <c r="A10" t="s">
+        <v>286</v>
+      </c>
+      <c r="B10" t="s">
         <v>287</v>
       </c>
-      <c r="B10" t="s">
+      <c r="C10" t="s">
         <v>288</v>
       </c>
-      <c r="C10" t="s">
+      <c r="D10" t="s">
         <v>289</v>
       </c>
-      <c r="D10" t="s">
+      <c r="E10" t="s">
         <v>290</v>
       </c>
-      <c r="E10" t="s">
+      <c r="F10" t="s">
         <v>291</v>
-      </c>
-      <c r="F10" t="s">
-        <v>292</v>
       </c>
     </row>
     <row r="11" ht="60" spans="1:6">
       <c r="A11" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B11" t="s">
+        <v>292</v>
+      </c>
+      <c r="C11" t="s">
         <v>293</v>
       </c>
-      <c r="C11" t="s">
+      <c r="D11" t="s">
         <v>294</v>
       </c>
-      <c r="D11" t="s">
+      <c r="E11" t="s">
         <v>295</v>
       </c>
-      <c r="E11" t="s">
+      <c r="F11" t="s">
         <v>296</v>
-      </c>
-      <c r="F11" t="s">
-        <v>297</v>
       </c>
     </row>
     <row r="12" ht="58.5" spans="1:6">
       <c r="A12" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B12" t="s">
+        <v>297</v>
+      </c>
+      <c r="C12" t="s">
         <v>298</v>
       </c>
-      <c r="C12" t="s">
+      <c r="D12" t="s">
         <v>299</v>
       </c>
-      <c r="D12" t="s">
+      <c r="E12" t="s">
         <v>300</v>
       </c>
-      <c r="E12" t="s">
+      <c r="F12" t="s">
         <v>301</v>
-      </c>
-      <c r="F12" t="s">
-        <v>302</v>
       </c>
     </row>
     <row r="13" ht="58.5" spans="1:6">
       <c r="A13" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B13" t="s">
+        <v>302</v>
+      </c>
+      <c r="C13" t="s">
         <v>303</v>
       </c>
-      <c r="C13" t="s">
+      <c r="D13" t="s">
         <v>304</v>
       </c>
-      <c r="D13" t="s">
+      <c r="E13" t="s">
         <v>305</v>
       </c>
-      <c r="E13" t="s">
+      <c r="F13" t="s">
         <v>306</v>
-      </c>
-      <c r="F13" t="s">
-        <v>307</v>
       </c>
     </row>
     <row r="14" ht="58.5" spans="1:6">
       <c r="A14" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B14" t="s">
+        <v>307</v>
+      </c>
+      <c r="C14" t="s">
         <v>308</v>
       </c>
-      <c r="C14" t="s">
+      <c r="D14" t="s">
         <v>309</v>
       </c>
-      <c r="D14" t="s">
+      <c r="E14" t="s">
         <v>310</v>
       </c>
-      <c r="E14" t="s">
+      <c r="F14" t="s">
         <v>311</v>
-      </c>
-      <c r="F14" t="s">
-        <v>312</v>
       </c>
     </row>
     <row r="15" ht="58.5" spans="1:6">
       <c r="A15" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B15" t="s">
+        <v>312</v>
+      </c>
+      <c r="C15" t="s">
         <v>313</v>
       </c>
-      <c r="C15" t="s">
+      <c r="D15" t="s">
         <v>314</v>
       </c>
-      <c r="D15" t="s">
+      <c r="E15" t="s">
         <v>315</v>
       </c>
-      <c r="E15" t="s">
+      <c r="F15" t="s">
         <v>316</v>
-      </c>
-      <c r="F15" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="16" ht="58.5" spans="1:6">
       <c r="A16" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B16" t="s">
+        <v>317</v>
+      </c>
+      <c r="C16" t="s">
         <v>318</v>
       </c>
-      <c r="C16" t="s">
+      <c r="D16" t="s">
         <v>319</v>
       </c>
-      <c r="D16" t="s">
+      <c r="E16" t="s">
         <v>320</v>
       </c>
-      <c r="E16" t="s">
+      <c r="F16" t="s">
         <v>321</v>
-      </c>
-      <c r="F16" t="s">
-        <v>322</v>
       </c>
     </row>
     <row r="17" ht="58.5" spans="1:6">
       <c r="A17" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B17" t="s">
+        <v>322</v>
+      </c>
+      <c r="C17" t="s">
         <v>323</v>
       </c>
-      <c r="C17" t="s">
+      <c r="D17" t="s">
         <v>324</v>
       </c>
-      <c r="D17" t="s">
+      <c r="E17" t="s">
         <v>325</v>
       </c>
-      <c r="E17" t="s">
+      <c r="F17" t="s">
         <v>326</v>
-      </c>
-      <c r="F17" t="s">
-        <v>327</v>
       </c>
     </row>
     <row r="18" ht="58.5" spans="1:6">
       <c r="A18" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B18" t="s">
+        <v>327</v>
+      </c>
+      <c r="C18" t="s">
         <v>328</v>
       </c>
-      <c r="C18" t="s">
+      <c r="D18" t="s">
         <v>329</v>
       </c>
-      <c r="D18" t="s">
+      <c r="E18" t="s">
         <v>330</v>
       </c>
-      <c r="E18" t="s">
+      <c r="F18" t="s">
         <v>331</v>
-      </c>
-      <c r="F18" t="s">
-        <v>332</v>
       </c>
     </row>
     <row r="19" ht="58.5" spans="1:6">
       <c r="A19" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B19" t="s">
+        <v>332</v>
+      </c>
+      <c r="C19" t="s">
         <v>333</v>
       </c>
-      <c r="C19" t="s">
+      <c r="D19" t="s">
         <v>334</v>
       </c>
-      <c r="D19" t="s">
+      <c r="E19" t="s">
         <v>335</v>
       </c>
-      <c r="E19" t="s">
+      <c r="F19" t="s">
         <v>336</v>
-      </c>
-      <c r="F19" t="s">
-        <v>337</v>
       </c>
     </row>
     <row r="20" ht="72" spans="1:6">
       <c r="A20" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B20" t="s">
+        <v>337</v>
+      </c>
+      <c r="C20" t="s">
         <v>338</v>
       </c>
-      <c r="C20" t="s">
+      <c r="D20" t="s">
         <v>339</v>
       </c>
-      <c r="D20" t="s">
+      <c r="E20" t="s">
         <v>340</v>
       </c>
-      <c r="E20" t="s">
+      <c r="F20" t="s">
         <v>341</v>
-      </c>
-      <c r="F20" t="s">
-        <v>342</v>
       </c>
     </row>
     <row r="21" ht="58.5" spans="1:6">
       <c r="A21" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B21" t="s">
+        <v>342</v>
+      </c>
+      <c r="C21" t="s">
         <v>343</v>
       </c>
-      <c r="C21" t="s">
+      <c r="D21" t="s">
         <v>344</v>
       </c>
-      <c r="D21" t="s">
+      <c r="E21" t="s">
         <v>345</v>
       </c>
-      <c r="E21" t="s">
+      <c r="F21" t="s">
         <v>346</v>
-      </c>
-      <c r="F21" t="s">
-        <v>347</v>
       </c>
     </row>
     <row r="22" ht="58.5" spans="1:6">
       <c r="A22" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B22" t="s">
+        <v>347</v>
+      </c>
+      <c r="C22" t="s">
         <v>348</v>
       </c>
-      <c r="C22" t="s">
+      <c r="D22" t="s">
         <v>349</v>
       </c>
-      <c r="D22" t="s">
+      <c r="E22" t="s">
         <v>350</v>
       </c>
-      <c r="E22" t="s">
+      <c r="F22" t="s">
         <v>351</v>
-      </c>
-      <c r="F22" t="s">
-        <v>352</v>
       </c>
     </row>
     <row r="23" ht="58.5" spans="1:6">
       <c r="A23" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B23" t="s">
+        <v>352</v>
+      </c>
+      <c r="C23" t="s">
         <v>353</v>
       </c>
-      <c r="C23" t="s">
+      <c r="D23" t="s">
         <v>354</v>
       </c>
-      <c r="D23" t="s">
+      <c r="E23" t="s">
         <v>355</v>
       </c>
-      <c r="E23" t="s">
+      <c r="F23" t="s">
         <v>356</v>
-      </c>
-      <c r="F23" t="s">
-        <v>357</v>
       </c>
     </row>
     <row r="24" ht="58.5" spans="1:6">
       <c r="A24" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B24" t="s">
+        <v>357</v>
+      </c>
+      <c r="C24" t="s">
         <v>358</v>
       </c>
-      <c r="C24" t="s">
+      <c r="D24" t="s">
+        <v>299</v>
+      </c>
+      <c r="E24" t="s">
         <v>359</v>
       </c>
-      <c r="D24" t="s">
-        <v>300</v>
-      </c>
-      <c r="E24" t="s">
+      <c r="F24" t="s">
         <v>360</v>
-      </c>
-      <c r="F24" t="s">
-        <v>361</v>
       </c>
     </row>
     <row r="25" ht="90" spans="1:6">
       <c r="A25" t="s">
+        <v>361</v>
+      </c>
+      <c r="B25" t="s">
         <v>362</v>
       </c>
-      <c r="B25" t="s">
+      <c r="C25" t="s">
         <v>363</v>
       </c>
-      <c r="C25" t="s">
+      <c r="D25" t="s">
         <v>364</v>
       </c>
-      <c r="D25" t="s">
+      <c r="E25" t="s">
         <v>365</v>
       </c>
-      <c r="E25" t="s">
+      <c r="F25" t="s">
         <v>366</v>
-      </c>
-      <c r="F25" t="s">
-        <v>367</v>
       </c>
     </row>
     <row r="26" ht="58.5" spans="1:6">
       <c r="A26" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B26" t="s">
+        <v>367</v>
+      </c>
+      <c r="C26" t="s">
         <v>368</v>
       </c>
-      <c r="C26" t="s">
+      <c r="D26" t="s">
         <v>369</v>
       </c>
-      <c r="D26" t="s">
+      <c r="E26" t="s">
         <v>370</v>
       </c>
-      <c r="E26" t="s">
+      <c r="F26" t="s">
         <v>371</v>
-      </c>
-      <c r="F26" t="s">
-        <v>372</v>
       </c>
     </row>
     <row r="27" ht="58.5" spans="1:6">
       <c r="A27" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B27" t="s">
+        <v>372</v>
+      </c>
+      <c r="C27" t="s">
         <v>373</v>
       </c>
-      <c r="C27" t="s">
+      <c r="D27" t="s">
         <v>374</v>
       </c>
-      <c r="D27" t="s">
+      <c r="E27" t="s">
         <v>375</v>
       </c>
-      <c r="E27" t="s">
+      <c r="F27" t="s">
         <v>376</v>
-      </c>
-      <c r="F27" t="s">
-        <v>377</v>
       </c>
     </row>
     <row r="28" ht="58.5" spans="1:6">
       <c r="A28" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B28" t="s">
+        <v>377</v>
+      </c>
+      <c r="C28" t="s">
         <v>378</v>
       </c>
-      <c r="C28" t="s">
+      <c r="D28" t="s">
+        <v>374</v>
+      </c>
+      <c r="E28" t="s">
         <v>379</v>
       </c>
-      <c r="D28" t="s">
-        <v>375</v>
-      </c>
-      <c r="E28" t="s">
+      <c r="F28" t="s">
         <v>380</v>
-      </c>
-      <c r="F28" t="s">
-        <v>381</v>
       </c>
     </row>
     <row r="29" ht="73.5" spans="1:6">
       <c r="A29" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B29" t="s">
+        <v>381</v>
+      </c>
+      <c r="C29" t="s">
         <v>382</v>
       </c>
-      <c r="C29" t="s">
+      <c r="D29" t="s">
         <v>383</v>
       </c>
-      <c r="D29" t="s">
+      <c r="E29" t="s">
         <v>384</v>
       </c>
-      <c r="E29" t="s">
+      <c r="F29" t="s">
         <v>385</v>
-      </c>
-      <c r="F29" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="30" ht="58.5" spans="1:6">
       <c r="A30" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B30" t="s">
+        <v>386</v>
+      </c>
+      <c r="C30" t="s">
         <v>387</v>
       </c>
-      <c r="C30" t="s">
+      <c r="D30" t="s">
         <v>388</v>
       </c>
-      <c r="D30" t="s">
+      <c r="E30" t="s">
         <v>389</v>
       </c>
-      <c r="E30" t="s">
+      <c r="F30" t="s">
         <v>390</v>
-      </c>
-      <c r="F30" t="s">
-        <v>391</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" t="s">
+        <v>391</v>
+      </c>
+      <c r="B31" t="s">
         <v>392</v>
       </c>
-      <c r="B31" t="s">
+      <c r="C31" t="s">
         <v>393</v>
       </c>
-      <c r="C31" t="s">
+      <c r="D31" t="s">
         <v>394</v>
-      </c>
-      <c r="D31" t="s">
-        <v>395</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_clark4F(1).xlsx
+++ b/Assets/Resources/VNovelizerRes/ExcelVNScripts/sntzm_clark4F(1).xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="20685" windowHeight="11400"/>
+    <workbookView windowWidth="20385" windowHeight="10605"/>
   </bookViews>
   <sheets>
     <sheet name="圣诺汀之梦_克拉克线4层（上）" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1015" uniqueCount="395">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1015" uniqueCount="396">
   <si>
     <t>ID</t>
   </si>
@@ -88,6 +88,9 @@
   </si>
   <si>
     <t>false</t>
+  </si>
+  <si>
+    <t>unlockmusic(Music9)</t>
   </si>
   <si>
     <t>源类型=type:exeBC; 层级=0</t>
@@ -350,7 +353,54 @@
     <t>当时被你们袭击的是我，从那之后就一直被问各种问题。就算我后面提醒了你们它的危险性，但你们还是自信满满地放它进了暗室，不是吗？</t>
   </si>
   <si>
-    <t>源类型=type:txt_Sophia; 层级=12; wherelist={"wheretype":"1","wheredatas":[{"sortnum":"1","way":"=","conditions":[{"algorithm":"+","valuetype":"4","valuekey":"","valuedata":"试图活捉","dowlist4":[]}],"targets":[{"algorithm":"+","valuetype":"1","valuekey":"","valuedata":"0","dowlist4":[]}]}]}</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>源类型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">=type:txt_Sophia; </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>层级</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>=12; wherelist={"wheretype":"1","wheredatas":[{"sortnum":"1","way":"=","conditions":[{"algorithm":"+","valuetype":"4","valuekey":"","valuedata":"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>试图活捉</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>","dowlist4":[]}],"targets":[{"algorithm":"+","valuetype":"1","valuekey":"","valuedata":"1","dowlist4":[]}]}]}</t>
+    </r>
   </si>
   <si>
     <t>18</t>
@@ -473,7 +523,54 @@
     <t>jump(41)</t>
   </si>
   <si>
-    <t>源类型=type:txt_pb; 层级=26; wherelist={"wheretype":"1","wheredatas":[{"sortnum":"1","way":"=","conditions":[{"algorithm":"+","valuetype":"4","valuekey":"","valuedata":"试图活捉","dowlist4":[]}],"targets":[{"algorithm":"+","valuetype":"1","valuekey":"","valuedata":"1","dowlist4":[]}]}]}; gotomainline=41</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>源类型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">=type:txt_pb; </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>层级</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>=26; wherelist={"wheretype":"1","wheredatas":[{"sortnum":"1","way":"=","conditions":[{"algorithm":"+","valuetype":"4","valuekey":"","valuedata":"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>试图活捉</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>","dowlist4":[]}],"targets":[{"algorithm":"+","valuetype":"1","valuekey":"","valuedata":"1","dowlist4":[]}]}]}; gotomainline=41</t>
+    </r>
   </si>
   <si>
     <t>33</t>
@@ -482,7 +579,54 @@
     <t>留下抓痕的小腿一瘸一拐地杵在克拉克身后，目光飞速扫视着周围的房间。</t>
   </si>
   <si>
-    <t>源类型=type:txt_pb; 层级=26; wherelist={"wheretype":"1","wheredatas":[{"sortnum":"1","way":"=","conditions":[{"algorithm":"+","valuetype":"4","valuekey":"","valuedata":"先发制人","dowlist4":[]}],"targets":[{"algorithm":"+","valuetype":"1","valuekey":"","valuedata":"1","dowlist4":[]}]}]}; gotomainline=41</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>源类型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">=type:txt_pb; </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>层级</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>=26; wherelist={"wheretype":"1","wheredatas":[{"sortnum":"1","way":"=","conditions":[{"algorithm":"+","valuetype":"4","valuekey":"","valuedata":"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>先发制人</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>","dowlist4":[]}],"targets":[{"algorithm":"+","valuetype":"1","valuekey":"","valuedata":"1","dowlist4":[]}]}]}; gotomainline=41</t>
+    </r>
   </si>
   <si>
     <t>21</t>
@@ -805,7 +949,54 @@
     <t>不到半分钟的功夫，你们便来到了四楼空旷无人的半露天平台上。四周的环境安静得有些发冷，一路上畅通无阻的顺利，反而让你们不自觉绷紧了神经。</t>
   </si>
   <si>
-    <t>源类型=type:txt_pb; 层级=1; wherelist={"wheretype":"1","wheredatas":[{"sortnum":"1","way":"=","conditions":[{"algorithm":"+","valuetype":"4","valuekey":"","valuedata":"无视飞蛾（克拉克）","dowlist4":[]}],"targets":[{"algorithm":"+","valuetype":"1","valuekey":"","valuedata":"0","dowlist4":[]}]}]}</t>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>源类型</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">=type:txt_pb; </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>层级</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>=1; wherelist={"wheretype":"1","wheredatas":[{"sortnum":"1","way":"=","conditions":[{"algorithm":"+","valuetype":"4","valuekey":"","valuedata":"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>无视飞蛾（克拉克）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>","dowlist4":[]}],"targets":[{"algorithm":"+","valuetype":"1","valuekey":"","valuedata":"1","dowlist4":[]}]}]}</t>
+    </r>
   </si>
   <si>
     <t>66</t>
@@ -2639,18 +2830,18 @@
         <v>17</v>
       </c>
       <c r="K2" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="L2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="3" ht="90" spans="1:12">
       <c r="A3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C3" t="s">
         <v>14</v>
@@ -2665,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="G3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="H3" t="s">
         <v>15</v>
       </c>
       <c r="I3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J3" t="s">
         <v>15</v>
@@ -2680,12 +2871,12 @@
         <v>15</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:12">
       <c r="A4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B4" t="s">
         <v>13</v>
@@ -2718,12 +2909,12 @@
         <v>15</v>
       </c>
       <c r="L4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5" ht="150" spans="1:12">
       <c r="A5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B5" t="s">
         <v>13</v>
@@ -2741,7 +2932,7 @@
         <v>15</v>
       </c>
       <c r="G5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H5" t="s">
         <v>15</v>
@@ -2756,12 +2947,12 @@
         <v>15</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6" ht="54" spans="1:12">
       <c r="A6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B6" t="s">
         <v>13</v>
@@ -2779,7 +2970,7 @@
         <v>15</v>
       </c>
       <c r="G6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="H6" t="s">
         <v>15</v>
@@ -2791,24 +2982,24 @@
         <v>15</v>
       </c>
       <c r="K6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" ht="150" spans="1:12">
       <c r="A7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C7" t="s">
         <v>14</v>
       </c>
       <c r="D7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E7" t="s">
         <v>15</v>
@@ -2817,7 +3008,7 @@
         <v>15</v>
       </c>
       <c r="G7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H7" t="s">
         <v>15</v>
@@ -2829,24 +3020,24 @@
         <v>15</v>
       </c>
       <c r="K7" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="8" ht="30" spans="1:12">
       <c r="A8" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B8" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C8" t="s">
         <v>14</v>
       </c>
       <c r="D8" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E8" t="s">
         <v>15</v>
@@ -2855,7 +3046,7 @@
         <v>15</v>
       </c>
       <c r="G8" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H8" t="s">
         <v>15</v>
@@ -2867,15 +3058,15 @@
         <v>15</v>
       </c>
       <c r="K8" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="L8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="9" ht="54" spans="1:12">
       <c r="A9" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B9" t="s">
         <v>13</v>
@@ -2893,7 +3084,7 @@
         <v>15</v>
       </c>
       <c r="G9" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="H9" t="s">
         <v>15</v>
@@ -2908,21 +3099,21 @@
         <v>15</v>
       </c>
       <c r="L9" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="10" ht="30" spans="1:12">
       <c r="A10" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B10" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C10" t="s">
         <v>14</v>
       </c>
       <c r="D10" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E10" t="s">
         <v>15</v>
@@ -2931,7 +3122,7 @@
         <v>15</v>
       </c>
       <c r="G10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H10" t="s">
         <v>15</v>
@@ -2943,15 +3134,15 @@
         <v>15</v>
       </c>
       <c r="K10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L10" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="11" ht="54" spans="1:12">
       <c r="A11" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B11" t="s">
         <v>13</v>
@@ -2960,7 +3151,7 @@
         <v>14</v>
       </c>
       <c r="D11" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E11" t="s">
         <v>15</v>
@@ -2969,7 +3160,7 @@
         <v>15</v>
       </c>
       <c r="G11" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="H11" t="s">
         <v>15</v>
@@ -2981,24 +3172,24 @@
         <v>15</v>
       </c>
       <c r="K11" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="L11" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="12" ht="27" spans="1:12">
       <c r="A12" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B12" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C12" t="s">
         <v>14</v>
       </c>
       <c r="D12" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E12" t="s">
         <v>15</v>
@@ -3007,7 +3198,7 @@
         <v>15</v>
       </c>
       <c r="G12" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="H12" t="s">
         <v>15</v>
@@ -3019,24 +3210,24 @@
         <v>15</v>
       </c>
       <c r="K12" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L12" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="13" ht="27" spans="1:12">
       <c r="A13" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B13" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C13" t="s">
         <v>14</v>
       </c>
       <c r="D13" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E13" t="s">
         <v>15</v>
@@ -3045,7 +3236,7 @@
         <v>15</v>
       </c>
       <c r="G13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H13" t="s">
         <v>15</v>
@@ -3060,12 +3251,12 @@
         <v>15</v>
       </c>
       <c r="L13" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14" ht="27" spans="1:12">
       <c r="A14" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B14" t="s">
         <v>13</v>
@@ -3074,7 +3265,7 @@
         <v>14</v>
       </c>
       <c r="D14" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E14" t="s">
         <v>15</v>
@@ -3083,7 +3274,7 @@
         <v>15</v>
       </c>
       <c r="G14" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H14" t="s">
         <v>15</v>
@@ -3095,15 +3286,15 @@
         <v>15</v>
       </c>
       <c r="K14" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="L14" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="15" spans="1:12">
       <c r="A15" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B15" t="s">
         <v>13</v>
@@ -3136,21 +3327,21 @@
         <v>15</v>
       </c>
       <c r="L15" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="16" ht="90" spans="1:12">
       <c r="A16" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B16" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C16" t="s">
         <v>14</v>
       </c>
       <c r="D16" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E16" t="s">
         <v>15</v>
@@ -3159,7 +3350,7 @@
         <v>15</v>
       </c>
       <c r="G16" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H16" t="s">
         <v>15</v>
@@ -3171,15 +3362,15 @@
         <v>15</v>
       </c>
       <c r="K16" t="s">
-        <v>37</v>
-      </c>
-      <c r="L16" t="s">
-        <v>68</v>
+        <v>38</v>
+      </c>
+      <c r="L16" s="2" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="17" ht="30" spans="1:12">
       <c r="A17" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B17" t="s">
         <v>13</v>
@@ -3188,7 +3379,7 @@
         <v>14</v>
       </c>
       <c r="D17" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E17" t="s">
         <v>15</v>
@@ -3197,7 +3388,7 @@
         <v>15</v>
       </c>
       <c r="G17" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H17" t="s">
         <v>15</v>
@@ -3209,15 +3400,15 @@
         <v>15</v>
       </c>
       <c r="K17" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="L17" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="18" ht="45" spans="1:12">
       <c r="A18" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B18" t="s">
         <v>13</v>
@@ -3247,15 +3438,15 @@
         <v>15</v>
       </c>
       <c r="K18" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="L18" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="19" spans="1:12">
       <c r="A19" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B19" t="s">
         <v>13</v>
@@ -3288,15 +3479,15 @@
         <v>15</v>
       </c>
       <c r="L19" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="20" ht="42" spans="1:12">
       <c r="A20" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B20" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C20" t="s">
         <v>14</v>
@@ -3311,7 +3502,7 @@
         <v>15</v>
       </c>
       <c r="G20" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H20" t="s">
         <v>15</v>
@@ -3326,21 +3517,21 @@
         <v>15</v>
       </c>
       <c r="L20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="21" ht="30" spans="1:12">
       <c r="A21" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B21" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C21" t="s">
         <v>14</v>
       </c>
       <c r="D21" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E21" t="s">
         <v>15</v>
@@ -3349,7 +3540,7 @@
         <v>15</v>
       </c>
       <c r="G21" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H21" t="s">
         <v>15</v>
@@ -3361,15 +3552,15 @@
         <v>15</v>
       </c>
       <c r="K21" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L21" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="22" ht="40.5" spans="1:12">
       <c r="A22" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B22" t="s">
         <v>13</v>
@@ -3378,7 +3569,7 @@
         <v>14</v>
       </c>
       <c r="D22" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E22" t="s">
         <v>15</v>
@@ -3387,7 +3578,7 @@
         <v>15</v>
       </c>
       <c r="G22" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="H22" t="s">
         <v>15</v>
@@ -3399,18 +3590,18 @@
         <v>15</v>
       </c>
       <c r="K22" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="L22" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="23" ht="57" spans="1:12">
       <c r="A23" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B23" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C23" t="s">
         <v>14</v>
@@ -3425,7 +3616,7 @@
         <v>15</v>
       </c>
       <c r="G23" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H23" t="s">
         <v>15</v>
@@ -3440,12 +3631,12 @@
         <v>15</v>
       </c>
       <c r="L23" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="24" ht="27" spans="1:12">
       <c r="A24" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B24" t="s">
         <v>13</v>
@@ -3463,7 +3654,7 @@
         <v>15</v>
       </c>
       <c r="G24" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H24" t="s">
         <v>15</v>
@@ -3478,15 +3669,15 @@
         <v>15</v>
       </c>
       <c r="L24" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="25" spans="1:12">
       <c r="A25" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B25" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C25" t="s">
         <v>14</v>
@@ -3501,7 +3692,7 @@
         <v>15</v>
       </c>
       <c r="G25" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H25" t="s">
         <v>15</v>
@@ -3516,15 +3707,15 @@
         <v>15</v>
       </c>
       <c r="L25" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="26" spans="1:12">
       <c r="A26" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B26" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C26" t="s">
         <v>14</v>
@@ -3539,7 +3730,7 @@
         <v>15</v>
       </c>
       <c r="G26" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="H26" t="s">
         <v>15</v>
@@ -3554,12 +3745,12 @@
         <v>15</v>
       </c>
       <c r="L26" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="27" ht="40.5" spans="1:12">
       <c r="A27" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B27" t="s">
         <v>13</v>
@@ -3577,7 +3768,7 @@
         <v>15</v>
       </c>
       <c r="G27" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H27" t="s">
         <v>15</v>
@@ -3592,12 +3783,12 @@
         <v>15</v>
       </c>
       <c r="L27" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="28" ht="27" spans="1:12">
       <c r="A28" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B28" t="s">
         <v>13</v>
@@ -3615,7 +3806,7 @@
         <v>15</v>
       </c>
       <c r="G28" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H28" t="s">
         <v>15</v>
@@ -3630,12 +3821,12 @@
         <v>15</v>
       </c>
       <c r="L28" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="29" spans="1:12">
       <c r="A29" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B29" t="s">
         <v>13</v>
@@ -3668,12 +3859,12 @@
         <v>15</v>
       </c>
       <c r="L29" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="30" ht="90" spans="1:12">
       <c r="A30" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B30" t="s">
         <v>13</v>
@@ -3691,7 +3882,7 @@
         <v>15</v>
       </c>
       <c r="G30" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H30" t="s">
         <v>15</v>
@@ -3703,15 +3894,15 @@
         <v>15</v>
       </c>
       <c r="K30" t="s">
-        <v>108</v>
-      </c>
-      <c r="L30" t="s">
         <v>109</v>
+      </c>
+      <c r="L30" s="2" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="31" ht="90" spans="1:12">
       <c r="A31" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B31" t="s">
         <v>13</v>
@@ -3729,7 +3920,7 @@
         <v>15</v>
       </c>
       <c r="G31" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="H31" t="s">
         <v>15</v>
@@ -3741,15 +3932,15 @@
         <v>15</v>
       </c>
       <c r="K31" t="s">
-        <v>108</v>
-      </c>
-      <c r="L31" t="s">
-        <v>112</v>
+        <v>109</v>
+      </c>
+      <c r="L31" s="2" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="32" spans="1:12">
       <c r="A32" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B32" t="s">
         <v>13</v>
@@ -3782,15 +3973,15 @@
         <v>15</v>
       </c>
       <c r="L32" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="33" ht="54" spans="1:12">
       <c r="A33" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B33" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C33" t="s">
         <v>14</v>
@@ -3805,7 +3996,7 @@
         <v>15</v>
       </c>
       <c r="G33" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H33" t="s">
         <v>15</v>
@@ -3820,12 +4011,12 @@
         <v>15</v>
       </c>
       <c r="L33" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="34" ht="54" spans="1:12">
       <c r="A34" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B34" t="s">
         <v>13</v>
@@ -3843,7 +4034,7 @@
         <v>15</v>
       </c>
       <c r="G34" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="H34" t="s">
         <v>15</v>
@@ -3858,21 +4049,21 @@
         <v>15</v>
       </c>
       <c r="L34" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="35" ht="40.5" spans="1:12">
       <c r="A35" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B35" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C35" t="s">
         <v>14</v>
       </c>
       <c r="D35" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E35" t="s">
         <v>15</v>
@@ -3881,7 +4072,7 @@
         <v>15</v>
       </c>
       <c r="G35" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H35" t="s">
         <v>15</v>
@@ -3893,24 +4084,24 @@
         <v>15</v>
       </c>
       <c r="K35" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L35" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="36" ht="30" spans="1:12">
       <c r="A36" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B36" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C36" t="s">
         <v>14</v>
       </c>
       <c r="D36" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E36" t="s">
         <v>15</v>
@@ -3919,7 +4110,7 @@
         <v>15</v>
       </c>
       <c r="G36" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="H36" t="s">
         <v>15</v>
@@ -3934,12 +4125,12 @@
         <v>15</v>
       </c>
       <c r="L36" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="37" ht="54" spans="1:12">
       <c r="A37" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B37" t="s">
         <v>13</v>
@@ -3948,7 +4139,7 @@
         <v>14</v>
       </c>
       <c r="D37" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E37" t="s">
         <v>15</v>
@@ -3957,7 +4148,7 @@
         <v>15</v>
       </c>
       <c r="G37" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H37" t="s">
         <v>15</v>
@@ -3969,15 +4160,15 @@
         <v>15</v>
       </c>
       <c r="K37" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="L37" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="38" ht="40.5" spans="1:12">
       <c r="A38" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B38" t="s">
         <v>13</v>
@@ -3995,7 +4186,7 @@
         <v>15</v>
       </c>
       <c r="G38" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H38" t="s">
         <v>15</v>
@@ -4010,12 +4201,12 @@
         <v>15</v>
       </c>
       <c r="L38" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="39" ht="27" spans="1:12">
       <c r="A39" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B39" t="s">
         <v>13</v>
@@ -4033,7 +4224,7 @@
         <v>15</v>
       </c>
       <c r="G39" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H39" t="s">
         <v>15</v>
@@ -4045,15 +4236,15 @@
         <v>15</v>
       </c>
       <c r="K39" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="L39" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="40" ht="40.5" spans="1:12">
       <c r="A40" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B40" t="s">
         <v>13</v>
@@ -4071,7 +4262,7 @@
         <v>15</v>
       </c>
       <c r="G40" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H40" t="s">
         <v>15</v>
@@ -4086,12 +4277,12 @@
         <v>15</v>
       </c>
       <c r="L40" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="41" ht="43.5" spans="1:12">
       <c r="A41" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B41" t="s">
         <v>13</v>
@@ -4109,7 +4300,7 @@
         <v>15</v>
       </c>
       <c r="G41" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H41" t="s">
         <v>15</v>
@@ -4124,12 +4315,12 @@
         <v>15</v>
       </c>
       <c r="L41" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="42" spans="1:12">
       <c r="A42" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B42" t="s">
         <v>13</v>
@@ -4162,12 +4353,12 @@
         <v>15</v>
       </c>
       <c r="L42" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="43" ht="90" spans="1:12">
       <c r="A43" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B43" t="s">
         <v>13</v>
@@ -4185,7 +4376,7 @@
         <v>15</v>
       </c>
       <c r="G43" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H43" t="s">
         <v>15</v>
@@ -4197,15 +4388,15 @@
         <v>15</v>
       </c>
       <c r="K43" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="L43" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
     </row>
     <row r="44" ht="90" spans="1:12">
       <c r="A44" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B44" t="s">
         <v>13</v>
@@ -4223,7 +4414,7 @@
         <v>15</v>
       </c>
       <c r="G44" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H44" t="s">
         <v>15</v>
@@ -4238,21 +4429,21 @@
         <v>15</v>
       </c>
       <c r="L44" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="45" ht="40.5" spans="1:12">
       <c r="A45" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B45" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C45" t="s">
         <v>14</v>
       </c>
       <c r="D45" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E45" t="s">
         <v>15</v>
@@ -4261,7 +4452,7 @@
         <v>15</v>
       </c>
       <c r="G45" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H45" t="s">
         <v>15</v>
@@ -4276,12 +4467,12 @@
         <v>15</v>
       </c>
       <c r="L45" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="46" ht="30" spans="1:12">
       <c r="A46" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B46" t="s">
         <v>13</v>
@@ -4290,7 +4481,7 @@
         <v>14</v>
       </c>
       <c r="D46" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E46" t="s">
         <v>15</v>
@@ -4299,7 +4490,7 @@
         <v>15</v>
       </c>
       <c r="G46" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H46" t="s">
         <v>15</v>
@@ -4311,21 +4502,21 @@
         <v>15</v>
       </c>
       <c r="L46" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="47" ht="30" spans="1:12">
       <c r="A47" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B47" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C47" t="s">
         <v>14</v>
       </c>
       <c r="D47" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E47" t="s">
         <v>15</v>
@@ -4334,7 +4525,7 @@
         <v>15</v>
       </c>
       <c r="G47" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H47" t="s">
         <v>15</v>
@@ -4346,15 +4537,15 @@
         <v>15</v>
       </c>
       <c r="K47" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="L47" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="48" ht="90" spans="1:12">
       <c r="A48" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B48" t="s">
         <v>13</v>
@@ -4363,7 +4554,7 @@
         <v>14</v>
       </c>
       <c r="D48" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E48" t="s">
         <v>15</v>
@@ -4372,7 +4563,7 @@
         <v>15</v>
       </c>
       <c r="G48" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H48" t="s">
         <v>15</v>
@@ -4384,15 +4575,15 @@
         <v>15</v>
       </c>
       <c r="K48" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="L48" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="49" ht="40.5" spans="1:12">
       <c r="A49" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B49" t="s">
         <v>13</v>
@@ -4410,7 +4601,7 @@
         <v>15</v>
       </c>
       <c r="G49" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H49" t="s">
         <v>15</v>
@@ -4425,12 +4616,12 @@
         <v>15</v>
       </c>
       <c r="L49" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="50" ht="27" spans="1:12">
       <c r="A50" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B50" t="s">
         <v>13</v>
@@ -4448,7 +4639,7 @@
         <v>15</v>
       </c>
       <c r="G50" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H50" t="s">
         <v>15</v>
@@ -4463,12 +4654,12 @@
         <v>15</v>
       </c>
       <c r="L50" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="51" ht="40.5" spans="1:12">
       <c r="A51" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B51" t="s">
         <v>13</v>
@@ -4486,7 +4677,7 @@
         <v>15</v>
       </c>
       <c r="G51" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H51" t="s">
         <v>15</v>
@@ -4501,12 +4692,12 @@
         <v>15</v>
       </c>
       <c r="L51" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="52" ht="40.5" spans="1:12">
       <c r="A52" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B52" t="s">
         <v>13</v>
@@ -4524,7 +4715,7 @@
         <v>15</v>
       </c>
       <c r="G52" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H52" t="s">
         <v>15</v>
@@ -4536,18 +4727,18 @@
         <v>15</v>
       </c>
       <c r="K52" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="L52" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="53" spans="1:12">
       <c r="A53" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B53" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C53" t="s">
         <v>14</v>
@@ -4562,7 +4753,7 @@
         <v>15</v>
       </c>
       <c r="G53" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H53" t="s">
         <v>15</v>
@@ -4577,12 +4768,12 @@
         <v>15</v>
       </c>
       <c r="L53" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="54" ht="27" spans="1:12">
       <c r="A54" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B54" t="s">
         <v>13</v>
@@ -4600,7 +4791,7 @@
         <v>15</v>
       </c>
       <c r="G54" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H54" t="s">
         <v>15</v>
@@ -4615,12 +4806,12 @@
         <v>15</v>
       </c>
       <c r="L54" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="55" spans="1:12">
       <c r="A55" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B55" t="s">
         <v>13</v>
@@ -4653,12 +4844,12 @@
         <v>15</v>
       </c>
       <c r="L55" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="56" ht="90" spans="1:12">
       <c r="A56" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B56" t="s">
         <v>13</v>
@@ -4676,7 +4867,7 @@
         <v>15</v>
       </c>
       <c r="G56" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="H56" t="s">
         <v>15</v>
@@ -4691,12 +4882,12 @@
         <v>15</v>
       </c>
       <c r="L56" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="57" ht="40.5" spans="1:12">
       <c r="A57" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B57" t="s">
         <v>13</v>
@@ -4714,7 +4905,7 @@
         <v>15</v>
       </c>
       <c r="G57" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H57" t="s">
         <v>15</v>
@@ -4729,12 +4920,12 @@
         <v>15</v>
       </c>
       <c r="L57" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="58" ht="40.5" spans="1:12">
       <c r="A58" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B58" t="s">
         <v>13</v>
@@ -4752,7 +4943,7 @@
         <v>15</v>
       </c>
       <c r="G58" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H58" t="s">
         <v>15</v>
@@ -4767,12 +4958,12 @@
         <v>15</v>
       </c>
       <c r="L58" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="59" ht="55.5" spans="1:12">
       <c r="A59" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B59" t="s">
         <v>13</v>
@@ -4790,7 +4981,7 @@
         <v>15</v>
       </c>
       <c r="G59" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H59" t="s">
         <v>15</v>
@@ -4805,12 +4996,12 @@
         <v>15</v>
       </c>
       <c r="L59" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="60" ht="42" spans="1:12">
       <c r="A60" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B60" t="s">
         <v>13</v>
@@ -4828,7 +5019,7 @@
         <v>15</v>
       </c>
       <c r="G60" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H60" t="s">
         <v>15</v>
@@ -4843,12 +5034,12 @@
         <v>15</v>
       </c>
       <c r="L60" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
     </row>
     <row r="61" spans="1:12">
       <c r="A61" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B61" t="s">
         <v>13</v>
@@ -4866,7 +5057,7 @@
         <v>15</v>
       </c>
       <c r="G61" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="H61" t="s">
         <v>15</v>
@@ -4878,15 +5069,15 @@
         <v>15</v>
       </c>
       <c r="K61" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="L61" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="62" ht="42" spans="1:12">
       <c r="A62" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B62" t="s">
         <v>13</v>
@@ -4904,25 +5095,24 @@
         <v>15</v>
       </c>
       <c r="G62" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H62" t="s">
         <v>15</v>
       </c>
-      <c r="I62"/>
       <c r="J62" t="s">
         <v>15</v>
       </c>
       <c r="K62" s="3" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="L62" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="63" ht="90" spans="1:12">
       <c r="A63" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B63" t="s">
         <v>13</v>
@@ -4940,7 +5130,7 @@
         <v>15</v>
       </c>
       <c r="G63" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H63" t="s">
         <v>15</v>
@@ -4952,24 +5142,24 @@
         <v>15</v>
       </c>
       <c r="K63" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="L63" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
     </row>
     <row r="64" ht="90" spans="1:12">
       <c r="A64" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B64" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C64" t="s">
         <v>14</v>
       </c>
       <c r="D64" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E64" t="s">
         <v>15</v>
@@ -4978,7 +5168,7 @@
         <v>15</v>
       </c>
       <c r="G64" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H64" t="s">
         <v>15</v>
@@ -4990,15 +5180,15 @@
         <v>15</v>
       </c>
       <c r="K64" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L64" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="65" ht="90" spans="1:12">
       <c r="A65" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B65" t="s">
         <v>13</v>
@@ -5016,7 +5206,7 @@
         <v>15</v>
       </c>
       <c r="G65" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H65" t="s">
         <v>15</v>
@@ -5027,16 +5217,16 @@
       <c r="J65" t="s">
         <v>15</v>
       </c>
-      <c r="L65" t="s">
-        <v>212</v>
+      <c r="L65" s="2" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="66" spans="1:12">
       <c r="A66" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B66" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C66" t="s">
         <v>14</v>
@@ -5051,7 +5241,7 @@
         <v>15</v>
       </c>
       <c r="G66" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H66" t="s">
         <v>15</v>
@@ -5066,12 +5256,12 @@
         <v>15</v>
       </c>
       <c r="L66" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
     </row>
     <row r="67" ht="40.5" spans="1:12">
       <c r="A67" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B67" t="s">
         <v>13</v>
@@ -5089,7 +5279,7 @@
         <v>15</v>
       </c>
       <c r="G67" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H67" t="s">
         <v>15</v>
@@ -5101,10 +5291,10 @@
         <v>15</v>
       </c>
       <c r="K67" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L67" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
   </sheetData>
@@ -5125,39 +5315,39 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="2" ht="45" spans="1:2">
       <c r="A2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B3" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B4" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B5" t="s">
         <v>12</v>
@@ -5165,15 +5355,15 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="7" ht="27" spans="1:2">
       <c r="A7" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B7" t="s">
         <v>12</v>
@@ -5181,66 +5371,66 @@
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B8" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="9" ht="27" spans="1:2">
       <c r="A9" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="10" ht="75" spans="1:2">
       <c r="A10" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B10" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="11" ht="75" spans="1:2">
       <c r="A11" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B11" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="12" ht="57" spans="1:2">
       <c r="A12" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B12" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="13" ht="58.5" spans="1:2">
       <c r="A13" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B13" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="14" ht="60" spans="1:2">
       <c r="A14" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B14" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="15" ht="75" spans="1:2">
       <c r="A15" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B15" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
   </sheetData>
@@ -5262,616 +5452,616 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="2" ht="73.5" spans="1:6">
       <c r="A2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C2" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="D2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="E2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="F2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
     </row>
     <row r="3" ht="103.5" spans="1:6">
       <c r="A3" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B3" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C3" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D3" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="E3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="F3" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
     </row>
     <row r="4" ht="45" spans="1:6">
       <c r="A4" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B4" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C4" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="D4" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E4" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F4" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="5" ht="45" spans="1:6">
       <c r="A5" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B5" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C5" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D5" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E5" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F5" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="6" ht="45" spans="1:6">
       <c r="A6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B6" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C6" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="D6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="7" ht="75" spans="1:6">
       <c r="A7" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B7" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C7" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D7" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="E7" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F7" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="8" ht="45" spans="1:6">
       <c r="A8" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B8" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C8" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="D8" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="E8" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="F8" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="9" ht="45" spans="1:6">
       <c r="A9" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B9" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C9" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="D9" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="E9" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F9" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="10" ht="58.5" spans="1:6">
       <c r="A10" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B10" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C10" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="D10" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="E10" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="F10" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="11" ht="60" spans="1:6">
       <c r="A11" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B11" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="C11" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D11" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="E11" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="F11" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="12" ht="58.5" spans="1:6">
       <c r="A12" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B12" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C12" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="D12" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="E12" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F12" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="13" ht="58.5" spans="1:6">
       <c r="A13" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B13" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C13" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="D13" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="E13" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="F13" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="14" ht="58.5" spans="1:6">
       <c r="A14" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B14" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C14" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D14" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="E14" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="F14" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="15" ht="58.5" spans="1:6">
       <c r="A15" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B15" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C15" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="D15" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="E15" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="F15" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
     </row>
     <row r="16" ht="58.5" spans="1:6">
       <c r="A16" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B16" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C16" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="D16" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="E16" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="F16" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="17" ht="58.5" spans="1:6">
       <c r="A17" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B17" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C17" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="D17" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="E17" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="F17" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="18" ht="58.5" spans="1:6">
       <c r="A18" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B18" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C18" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="D18" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="E18" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="F18" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
     </row>
     <row r="19" ht="58.5" spans="1:6">
       <c r="A19" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B19" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C19" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="D19" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="E19" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="F19" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
     </row>
     <row r="20" ht="72" spans="1:6">
       <c r="A20" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B20" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C20" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="D20" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="E20" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="F20" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="21" ht="58.5" spans="1:6">
       <c r="A21" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B21" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C21" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="D21" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="E21" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="F21" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="22" ht="58.5" spans="1:6">
       <c r="A22" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B22" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C22" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="D22" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="E22" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="F22" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="23" ht="58.5" spans="1:6">
       <c r="A23" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B23" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C23" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D23" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="E23" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="F23" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="24" ht="58.5" spans="1:6">
       <c r="A24" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B24" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C24" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="D24" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="E24" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="F24" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="25" ht="90" spans="1:6">
       <c r="A25" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B25" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C25" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="D25" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="E25" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="F25" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="26" ht="58.5" spans="1:6">
       <c r="A26" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B26" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C26" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="D26" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="E26" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="F26" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="27" ht="58.5" spans="1:6">
       <c r="A27" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B27" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C27" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D27" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="E27" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="F27" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="28" ht="58.5" spans="1:6">
       <c r="A28" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B28" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C28" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="D28" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="E28" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="F28" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
     </row>
     <row r="29" ht="73.5" spans="1:6">
       <c r="A29" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B29" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C29" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="D29" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="E29" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="F29" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
     </row>
     <row r="30" ht="58.5" spans="1:6">
       <c r="A30" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B30" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C30" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="D30" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="E30" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="F30" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B31" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C31" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="D31" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
   </sheetData>
